--- a/data/trans_orig/P16A08-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258836</t>
+          <t>258301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270329</t>
+          <t>270357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251096</t>
+          <t>250540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259816</t>
+          <t>259783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514332</t>
+          <t>514963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528263</t>
+          <t>528368</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44799</t>
+          <t>42885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31288</t>
+          <t>30940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56274</t>
+          <t>57949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472901</t>
+          <t>473245</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487347</t>
+          <t>487326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459150</t>
+          <t>461064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482166</t>
+          <t>481608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>940750</t>
+          <t>939075</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>965736</t>
+          <t>966084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15529</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>19879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308703</t>
+          <t>309393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319883</t>
+          <t>319266</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331523</t>
+          <t>330767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634566</t>
+          <t>634379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648574</t>
+          <t>647854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>22813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>22399</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>14661</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>33046</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>2,01%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>22399</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>13632</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>33693</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340544</t>
+          <t>340344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354454</t>
+          <t>354312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349858</t>
+          <t>348643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363984</t>
+          <t>364204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>707728</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>697081</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>715466</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>97,99%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>707728</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>696434</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>716495</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10246</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26912</t>
+          <t>28453</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36955</t>
+          <t>36534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189648</t>
+          <t>190144</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200617</t>
+          <t>200459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180756</t>
+          <t>179215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197422</t>
+          <t>196973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374021</t>
+          <t>374442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395004</t>
+          <t>395203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>24870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259158</t>
+          <t>258670</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269201</t>
+          <t>269781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261300</t>
+          <t>261099</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273743</t>
+          <t>273605</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525122</t>
+          <t>524085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>541184</t>
+          <t>540873</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18250</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29380</t>
+          <t>27820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41044</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596777</t>
+          <t>597419</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610662</t>
+          <t>610585</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>608839</t>
+          <t>610399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>626603</t>
+          <t>627360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1212202</t>
+          <t>1212878</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1233404</t>
+          <t>1234430</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19041</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>41240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43403</t>
+          <t>43007</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>72510</t>
+          <t>74820</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>702731</t>
+          <t>701537</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723736</t>
+          <t>722963</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>742429</t>
+          <t>742918</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>763066</t>
+          <t>762988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1453778</t>
+          <t>1451468</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1482885</t>
+          <t>1483281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61545</t>
+          <t>61076</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>98468</t>
+          <t>96429</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>110742</t>
+          <t>110391</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>154949</t>
+          <t>157218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>180513</t>
+          <t>182254</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>242450</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3177057</t>
+          <t>3179096</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3213980</t>
+          <t>3214449</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3224248</t>
+          <t>3221979</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3268455</t>
+          <t>3268806</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6412272</t>
+          <t>6411768</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6474209</t>
+          <t>6472468</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>20737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>29582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20427</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44130</t>
+          <t>43932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271416</t>
+          <t>269466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285060</t>
+          <t>284305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250608</t>
+          <t>250761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268807</t>
+          <t>268121</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526416</t>
+          <t>526614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>550119</t>
+          <t>550691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>49227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26308</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50252</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53945</t>
+          <t>54225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90318</t>
+          <t>89346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>457466</t>
+          <t>456300</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>484623</t>
+          <t>483573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472479</t>
+          <t>471380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496423</t>
+          <t>495838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937940</t>
+          <t>938912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974313</t>
+          <t>974033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>36524</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44588</t>
+          <t>44558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309459</t>
+          <t>309977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320291</t>
+          <t>320230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305619</t>
+          <t>304496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324587</t>
+          <t>325532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619548</t>
+          <t>619578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642970</t>
+          <t>641836</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15061</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33045</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359481</t>
+          <t>358792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370987</t>
+          <t>370841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363161</t>
+          <t>362274</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>379234</t>
+          <t>378896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728911</t>
+          <t>728523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746895</t>
+          <t>746803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20620</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42417</t>
+          <t>40957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197079</t>
+          <t>196675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208496</t>
+          <t>208690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188598</t>
+          <t>188658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206265</t>
+          <t>205986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>389792</t>
+          <t>391252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411589</t>
+          <t>411460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15975</t>
+          <t>14940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35716</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253765</t>
+          <t>255649</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268941</t>
+          <t>268908</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254781</t>
+          <t>253960</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270057</t>
+          <t>270036</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516318</t>
+          <t>515572</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536059</t>
+          <t>537094</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>18263</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40968</t>
+          <t>41366</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27311</t>
+          <t>26870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>51554</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>644833</t>
+          <t>643897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>657855</t>
+          <t>657664</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>652885</t>
+          <t>652487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>674985</t>
+          <t>675590</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1303409</t>
+          <t>1305087</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1329330</t>
+          <t>1329771</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41763</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23933</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>47670</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48846</t>
+          <t>49958</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82510</t>
+          <t>82977</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>735209</t>
+          <t>735811</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>756927</t>
+          <t>758603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>774695</t>
+          <t>773850</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>797587</t>
+          <t>796791</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1515982</t>
+          <t>1515515</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1549646</t>
+          <t>1548534</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97114</t>
+          <t>94908</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>140864</t>
+          <t>139426</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169425</t>
+          <t>167870</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>224957</t>
+          <t>224586</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>274781</t>
+          <t>279694</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>349313</t>
+          <t>352409</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3278324</t>
+          <t>3279762</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3322074</t>
+          <t>3324280</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3320129</t>
+          <t>3320500</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3375661</t>
+          <t>3377216</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6614961</t>
+          <t>6611865</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6689493</t>
+          <t>6684580</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>19996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23154</t>
+          <t>22606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35734</t>
+          <t>34675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274093</t>
+          <t>273765</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287877</t>
+          <t>287807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265549</t>
+          <t>266097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281716</t>
+          <t>281413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546730</t>
+          <t>547789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>566322</t>
+          <t>567090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>23129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48985</t>
+          <t>49880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37211</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65704</t>
+          <t>63711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479746</t>
+          <t>479446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494423</t>
+          <t>494531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474099</t>
+          <t>473204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497409</t>
+          <t>496547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>959955</t>
+          <t>961948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>988448</t>
+          <t>990068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29363</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301863</t>
+          <t>301491</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314187</t>
+          <t>314029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318833</t>
+          <t>319337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330853</t>
+          <t>331538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625511</t>
+          <t>625628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642718</t>
+          <t>643081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27108</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>29498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56840</t>
+          <t>56884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342856</t>
+          <t>343839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361130</t>
+          <t>360910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350697</t>
+          <t>348865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371232</t>
+          <t>371192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700407</t>
+          <t>700363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728197</t>
+          <t>727749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201318</t>
+          <t>201119</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>209631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201674</t>
+          <t>201189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213279</t>
+          <t>213060</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>406924</t>
+          <t>406076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>421403</t>
+          <t>420906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>14744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34874</t>
+          <t>33605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245500</t>
+          <t>246362</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258208</t>
+          <t>258194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250673</t>
+          <t>250609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265918</t>
+          <t>266773</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501364</t>
+          <t>502633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521642</t>
+          <t>521494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27643</t>
+          <t>27939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54169</t>
+          <t>53164</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40207</t>
+          <t>39864</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>69779</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>631591</t>
+          <t>630179</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649045</t>
+          <t>648588</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637125</t>
+          <t>638130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>663651</t>
+          <t>663355</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275741</t>
+          <t>1278073</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1307645</t>
+          <t>1307988</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>16023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57536</t>
+          <t>56474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51457</t>
+          <t>52541</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84283</t>
+          <t>84961</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742399</t>
+          <t>742876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761873</t>
+          <t>762560</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>768631</t>
+          <t>769693</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>795310</t>
+          <t>795864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1520467</t>
+          <t>1519789</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1553293</t>
+          <t>1552209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85287</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>125454</t>
+          <t>126112</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>163880</t>
+          <t>165895</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>219774</t>
+          <t>218225</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>259786</t>
+          <t>262087</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>330773</t>
+          <t>332000</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3268896</t>
+          <t>3268238</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3309063</t>
+          <t>3309154</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3324768</t>
+          <t>3326317</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3380662</t>
+          <t>3378647</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6608119</t>
+          <t>6606892</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6679106</t>
+          <t>6676805</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38006</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44483</t>
+          <t>45840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273437</t>
+          <t>273256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300454</t>
+          <t>301291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280074</t>
+          <t>279476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286903</t>
+          <t>286848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556594</t>
+          <t>555237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586325</t>
+          <t>585553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41021</t>
+          <t>40356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37941</t>
+          <t>37288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38211</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70008</t>
+          <t>69819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476372</t>
+          <t>477037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503441</t>
+          <t>502739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475784</t>
+          <t>476437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493879</t>
+          <t>494364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>961110</t>
+          <t>961299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>992907</t>
+          <t>992999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>14386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>28674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294902</t>
+          <t>295699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311519</t>
+          <t>311750</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>335150</t>
+          <t>334742</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>344813</t>
+          <t>345116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636125</t>
+          <t>636014</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654221</t>
+          <t>654308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224331</t>
+          <t>229299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>281863</t>
+          <t>283787</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298482</t>
+          <t>297649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311212</t>
+          <t>310671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>251056</t>
+          <t>246088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465619</t>
+          <t>465680</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>506081</t>
+          <t>504157</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>773051</t>
+          <t>772545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165390</t>
+          <t>165553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175960</t>
+          <t>175844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195448</t>
+          <t>195381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203573</t>
+          <t>203868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365276</t>
+          <t>365259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377754</t>
+          <t>377874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>16797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255534</t>
+          <t>256213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266863</t>
+          <t>266568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239968</t>
+          <t>240259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251759</t>
+          <t>251903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>500322</t>
+          <t>501335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516961</t>
+          <t>516599</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26179</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23106</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68156</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39493</t>
+          <t>39128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83756</t>
+          <t>84593</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>598100</t>
+          <t>596363</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614297</t>
+          <t>614186</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>781109</t>
+          <t>781609</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>826159</t>
+          <t>826448</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1389788</t>
+          <t>1388951</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1434051</t>
+          <t>1434416</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37886</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33518</t>
+          <t>33611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54626</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39468</t>
+          <t>40817</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85434</t>
+          <t>85276</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>890834</t>
+          <t>891046</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>920224</t>
+          <t>920249</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>660225</t>
+          <t>660976</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>681333</t>
+          <t>681240</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1558138</t>
+          <t>1558296</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1604104</t>
+          <t>1602755</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>84475</t>
+          <t>83532</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>143314</t>
+          <t>141710</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>152869</t>
+          <t>153989</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>463207</t>
+          <t>503983</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>261143</t>
+          <t>263416</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>625379</t>
+          <t>574729</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3315016</t>
+          <t>3316620</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3373855</t>
+          <t>3374798</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3194495</t>
+          <t>3153719</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3504833</t>
+          <t>3503713</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6490653</t>
+          <t>6541303</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6854889</t>
+          <t>6852616</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A08-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>19791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258301</t>
+          <t>258894</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270357</t>
+          <t>270401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250540</t>
+          <t>251501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259783</t>
+          <t>259779</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514963</t>
+          <t>514057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528368</t>
+          <t>528921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42885</t>
+          <t>44496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30940</t>
+          <t>31180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57949</t>
+          <t>55924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473245</t>
+          <t>472845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487326</t>
+          <t>487220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461064</t>
+          <t>459453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>481608</t>
+          <t>481338</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939075</t>
+          <t>941100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>966084</t>
+          <t>965844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9343</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>16428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309393</t>
+          <t>309503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319266</t>
+          <t>318984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330767</t>
+          <t>331442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634379</t>
+          <t>635515</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647854</t>
+          <t>648668</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>6991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>20785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33046</t>
+          <t>34700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340344</t>
+          <t>340302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354312</t>
+          <t>354346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348643</t>
+          <t>350671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364204</t>
+          <t>364465</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697081</t>
+          <t>695427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715466</t>
+          <t>715763</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28453</t>
+          <t>28329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36534</t>
+          <t>36232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190144</t>
+          <t>189656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200459</t>
+          <t>200401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179215</t>
+          <t>179339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196973</t>
+          <t>197242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374442</t>
+          <t>374744</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395203</t>
+          <t>395558</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24870</t>
+          <t>25439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258670</t>
+          <t>259194</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261099</t>
+          <t>260536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273605</t>
+          <t>273259</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>524085</t>
+          <t>523516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540873</t>
+          <t>540319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27820</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40368</t>
+          <t>41060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>597419</t>
+          <t>597069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610585</t>
+          <t>610644</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>610399</t>
+          <t>609536</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>627360</t>
+          <t>626903</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1212878</t>
+          <t>1212186</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1234430</t>
+          <t>1234690</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41240</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>20254</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40593</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43007</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74820</t>
+          <t>75770</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>701537</t>
+          <t>701873</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>722963</t>
+          <t>723875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>742918</t>
+          <t>742064</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>762988</t>
+          <t>763257</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1451468</t>
+          <t>1450518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1483281</t>
+          <t>1482809</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61076</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96429</t>
+          <t>97361</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>110391</t>
+          <t>112128</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>157218</t>
+          <t>156802</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>182254</t>
+          <t>181916</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>242954</t>
+          <t>238183</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3179096</t>
+          <t>3178164</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3214449</t>
+          <t>3213719</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3221979</t>
+          <t>3222395</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3268806</t>
+          <t>3267069</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6411768</t>
+          <t>6416539</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6472468</t>
+          <t>6472806</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>31770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>43185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269466</t>
+          <t>271272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284305</t>
+          <t>285011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250761</t>
+          <t>248573</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268121</t>
+          <t>268140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526614</t>
+          <t>527361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>550691</t>
+          <t>550428</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49227</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>27102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54225</t>
+          <t>54836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89346</t>
+          <t>91965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456300</t>
+          <t>458594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>483573</t>
+          <t>484796</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471380</t>
+          <t>470356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495838</t>
+          <t>495629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>938912</t>
+          <t>936293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974033</t>
+          <t>973422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>22098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44558</t>
+          <t>45357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309977</t>
+          <t>309235</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320230</t>
+          <t>320245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>304496</t>
+          <t>306421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325532</t>
+          <t>325417</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619578</t>
+          <t>618779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641836</t>
+          <t>642038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25700</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33433</t>
+          <t>33572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358792</t>
+          <t>360150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370841</t>
+          <t>370869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362274</t>
+          <t>362818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378896</t>
+          <t>378393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728523</t>
+          <t>728384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746803</t>
+          <t>746855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30933</t>
+          <t>31486</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40957</t>
+          <t>41129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196675</t>
+          <t>197185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208690</t>
+          <t>208583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188658</t>
+          <t>188105</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205986</t>
+          <t>206239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391252</t>
+          <t>391080</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411460</t>
+          <t>411392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>24468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36462</t>
+          <t>37000</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255649</t>
+          <t>255886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268908</t>
+          <t>268813</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253960</t>
+          <t>253585</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270036</t>
+          <t>269980</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>515572</t>
+          <t>515034</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>537094</t>
+          <t>536064</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>41011</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51554</t>
+          <t>53360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643897</t>
+          <t>643916</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>657664</t>
+          <t>658496</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>652487</t>
+          <t>652842</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>675590</t>
+          <t>674692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1305087</t>
+          <t>1303281</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1329771</t>
+          <t>1328740</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>19387</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>41807</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47670</t>
+          <t>48687</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49958</t>
+          <t>48846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82977</t>
+          <t>79654</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>735811</t>
+          <t>735165</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>758603</t>
+          <t>757585</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>773850</t>
+          <t>772833</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>796791</t>
+          <t>797716</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1515515</t>
+          <t>1518838</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1548534</t>
+          <t>1549646</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>95064</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>139426</t>
+          <t>139924</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>167870</t>
+          <t>167255</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>224586</t>
+          <t>223801</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>279694</t>
+          <t>278194</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>352409</t>
+          <t>348033</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3279762</t>
+          <t>3279264</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3324280</t>
+          <t>3324124</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3320500</t>
+          <t>3321285</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3377216</t>
+          <t>3377831</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6611865</t>
+          <t>6616241</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6684580</t>
+          <t>6686080</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34675</t>
+          <t>35985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273765</t>
+          <t>274049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287807</t>
+          <t>287861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266097</t>
+          <t>266113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281413</t>
+          <t>281542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>547789</t>
+          <t>546479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567090</t>
+          <t>566663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>25976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>50149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>38326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63711</t>
+          <t>66051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479446</t>
+          <t>480062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494531</t>
+          <t>494567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473204</t>
+          <t>472935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496547</t>
+          <t>497108</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>961948</t>
+          <t>959608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990068</t>
+          <t>987333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>17530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29246</t>
+          <t>29052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301491</t>
+          <t>301415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314029</t>
+          <t>313970</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319337</t>
+          <t>318779</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331538</t>
+          <t>330848</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625628</t>
+          <t>625822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643081</t>
+          <t>643388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26125</t>
+          <t>24761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>37614</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>28441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56884</t>
+          <t>56004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343839</t>
+          <t>345203</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360910</t>
+          <t>360870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348865</t>
+          <t>349669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371192</t>
+          <t>371361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700363</t>
+          <t>701243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>727749</t>
+          <t>728806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>18383</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201119</t>
+          <t>201242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209631</t>
+          <t>209519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201189</t>
+          <t>200204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213060</t>
+          <t>212974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>406076</t>
+          <t>405714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>420906</t>
+          <t>420845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>24021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>34712</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246362</t>
+          <t>246776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258194</t>
+          <t>258413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250609</t>
+          <t>249094</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266773</t>
+          <t>266038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>502633</t>
+          <t>501526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521494</t>
+          <t>521274</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53164</t>
+          <t>52761</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,47 +9487,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>54460</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>41683</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>74126</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>4,04%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>54460</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>39864</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>69779</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630179</t>
+          <t>630902</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648588</t>
+          <t>648638</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>638130</t>
+          <t>638533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>663355</t>
+          <t>663030</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,47 +9600,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1293392</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1273726</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1306169</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>95,96%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1293392</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1278073</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1307988</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16023</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>29948</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56474</t>
+          <t>56124</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52541</t>
+          <t>51612</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84961</t>
+          <t>84919</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742876</t>
+          <t>742509</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>762560</t>
+          <t>761866</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>769693</t>
+          <t>770043</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>795864</t>
+          <t>796219</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1519789</t>
+          <t>1519831</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1552209</t>
+          <t>1553138</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85196</t>
+          <t>87399</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>126112</t>
+          <t>125072</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>165895</t>
+          <t>163853</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>218225</t>
+          <t>221970</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>262087</t>
+          <t>261314</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>332000</t>
+          <t>327835</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3268238</t>
+          <t>3269278</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3309154</t>
+          <t>3306951</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3326317</t>
+          <t>3322572</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3378647</t>
+          <t>3380689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6606892</t>
+          <t>6611057</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6676805</t>
+          <t>6677578</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19803</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>29447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45840</t>
+          <t>39527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>291640</t>
+          <t>302305</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273256</t>
+          <t>289398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301291</t>
+          <t>309019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>284181</t>
+          <t>306848</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279476</t>
+          <t>297188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286848</t>
+          <t>311241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>575821</t>
+          <t>609153</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555237</t>
+          <t>595379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>585553</t>
+          <t>618558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24436</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40356</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37288</t>
+          <t>39955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51764</t>
+          <t>53199</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69819</t>
+          <t>70272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>492957</t>
+          <t>505348</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477037</t>
+          <t>490230</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502739</t>
+          <t>515343</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>486397</t>
+          <t>516326</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476437</t>
+          <t>505258</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>494364</t>
+          <t>523803</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>979354</t>
+          <t>1021674</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>961299</t>
+          <t>1004601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>992999</t>
+          <t>1036024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17609</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28674</t>
+          <t>27219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>306118</t>
+          <t>305902</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295699</t>
+          <t>297032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311750</t>
+          <t>311206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>341081</t>
+          <t>348368</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334742</t>
+          <t>342588</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345116</t>
+          <t>351894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>647199</t>
+          <t>654271</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636014</t>
+          <t>644661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654308</t>
+          <t>660754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80245</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>229299</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>85930</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>283787</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>306872</t>
+          <t>365528</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>297649</t>
+          <t>354548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310671</t>
+          <t>370562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>395142</t>
+          <t>409178</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246088</t>
+          <t>398015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465680</t>
+          <t>414583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>702014</t>
+          <t>774706</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>504157</t>
+          <t>762224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>772545</t>
+          <t>782379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13189</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>24074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>172420</t>
+          <t>198987</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165553</t>
+          <t>192654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175844</t>
+          <t>202795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>200439</t>
+          <t>218449</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195381</t>
+          <t>213036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203868</t>
+          <t>221816</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>372860</t>
+          <t>417436</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365259</t>
+          <t>408805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377874</t>
+          <t>422905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16797</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,22 +12482,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25989</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>262732</t>
+          <t>264106</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256213</t>
+          <t>256785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266568</t>
+          <t>267723</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>247489</t>
+          <t>253820</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240259</t>
+          <t>247282</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251903</t>
+          <t>258567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,27 +12595,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>510221</t>
+          <t>517926</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501335</t>
+          <t>508468</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516599</t>
+          <t>524181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27916</t>
+          <t>34478</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>56657</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22817</t>
+          <t>44613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67656</t>
+          <t>72474</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>64168</t>
+          <t>78728</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39128</t>
+          <t>62975</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84593</t>
+          <t>98791</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>607475</t>
+          <t>697615</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596363</t>
+          <t>685209</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614186</t>
+          <t>705807</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>801901</t>
+          <t>715400</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>781609</t>
+          <t>699583</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>826448</t>
+          <t>727444</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1409376</t>
+          <t>1413016</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1388951</t>
+          <t>1392953</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1434416</t>
+          <t>1428769</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23284</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>39107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43461</t>
+          <t>51004</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33611</t>
+          <t>40406</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>65868</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>66745</t>
+          <t>77134</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40817</t>
+          <t>62619</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85276</t>
+          <t>94861</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>905436</t>
+          <t>771942</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>891046</t>
+          <t>758965</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>920249</t>
+          <t>780789</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>671390</t>
+          <t>779002</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>660976</t>
+          <t>764138</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>681240</t>
+          <t>789600</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1576827</t>
+          <t>1550944</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1558296</t>
+          <t>1533217</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1602755</t>
+          <t>1565459</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>112679</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>83532</t>
+          <t>99673</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>141710</t>
+          <t>146731</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>153989</t>
+          <t>162551</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>503983</t>
+          <t>211185</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>342361</t>
+          <t>304467</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>263416</t>
+          <t>273514</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>574729</t>
+          <t>339927</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3345651</t>
+          <t>3411735</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3316620</t>
+          <t>3384549</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3374798</t>
+          <t>3431607</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3428020</t>
+          <t>3547392</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3153719</t>
+          <t>3521128</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3503713</t>
+          <t>3569762</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6773671</t>
+          <t>6959126</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6541303</t>
+          <t>6923666</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6852616</t>
+          <t>6990079</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
